--- a/numerical-workflows/v2/framework/01_源表/节奏口径.xlsx
+++ b/numerical-workflows/v2/framework/01_源表/节奏口径.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\数值文档\数值文档\框架v2\01_源表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vgame_design\numerical-workflows\v2\framework\01_源表\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -117,7 +117,7 @@
     <t>舱室</t>
   </si>
   <si>
-    <t>资源副本-舱室</t>
+    <t>资源副本-舱室、温泉</t>
   </si>
   <si>
     <t>舱室养成需要建筑材料，可以从主线和高难主线刷取</t>
